--- a/fixtures/jeju/timetables/bis/raw/405026.xlsx
+++ b/fixtures/jeju/timetables/bis/raw/405026.xlsx
@@ -6,10 +6,10 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="320 (평일)하귀-한라대-연북로-탐라중-삼화지구" r:id="rId3" sheetId="1"/>
-    <sheet name="320 (평일)삼화지구-탐라중-연북로-한라대-하귀" r:id="rId4" sheetId="2"/>
-    <sheet name="320 (휴일)하귀-한라대-연북로-탐라중-삼화지구" r:id="rId5" sheetId="3"/>
-    <sheet name="320 (휴일)삼화지구-탐라중-연북로-한라대-하귀" r:id="rId6" sheetId="4"/>
+    <sheet name="320 (평일)삼화지구-탐라중-연북로-한라대-하귀" r:id="rId3" sheetId="1"/>
+    <sheet name="320 (평일)하귀-한라대-연북로-탐라중-삼화지구" r:id="rId4" sheetId="2"/>
+    <sheet name="320 (휴일)삼화지구-탐라중-연북로-한라대-하귀" r:id="rId5" sheetId="3"/>
+    <sheet name="320 (휴일)하귀-한라대-연북로-탐라중-삼화지구" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
@@ -20,788 +20,6 @@
     <t>구분</t>
   </si>
   <si>
-    <t>수산(하귀)</t>
-  </si>
-  <si>
-    <t>하귀휴먼시아</t>
-  </si>
-  <si>
-    <t>외도부영</t>
-  </si>
-  <si>
-    <t>롯데마트</t>
-  </si>
-  <si>
-    <t>제주여고(정문)</t>
-  </si>
-  <si>
-    <t>근로복지공단
-(연삼로)</t>
-  </si>
-  <si>
-    <t>화북휴먼시아</t>
-  </si>
-  <si>
-    <t>화북휴먼시아
- 정문</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>06:14
-(노형성당 출발)</t>
-  </si>
-  <si>
-    <t>06:21</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>06:51</t>
-  </si>
-  <si>
-    <t>07:03</t>
-  </si>
-  <si>
-    <t>07:11</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>06:37</t>
-  </si>
-  <si>
-    <t>07:01</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>07:43</t>
-  </si>
-  <si>
-    <t>07:51</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>07:09</t>
-  </si>
-  <si>
-    <t>07:33</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>08:03</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:23</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>07:22</t>
-  </si>
-  <si>
-    <t>07:48</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>08:32</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>07:19</t>
-  </si>
-  <si>
-    <t>07:32</t>
-  </si>
-  <si>
-    <t>07:58</t>
-  </si>
-  <si>
-    <t>08:19</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>08:42</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>07:37</t>
-  </si>
-  <si>
-    <t>08:24</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>08:47</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>07:18</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
-    <t>08:43</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>07:47</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>08:26</t>
-  </si>
-  <si>
-    <t>08:58</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:18</t>
-  </si>
-  <si>
-    <t>08:17
-(하귀하나로)</t>
-  </si>
-  <si>
-    <t>08:33</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>09:16</t>
-  </si>
-  <si>
-    <t>09:27</t>
-  </si>
-  <si>
-    <t>09:39</t>
-  </si>
-  <si>
-    <t>09:47</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>09:34</t>
-  </si>
-  <si>
-    <t>10:11</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>10:53</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>10:16</t>
-  </si>
-  <si>
-    <t>10:29</t>
-  </si>
-  <si>
-    <t>11:12</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>11:43</t>
-  </si>
-  <si>
-    <t>10:34</t>
-  </si>
-  <si>
-    <t>10:48</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:07</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:33</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>12:16</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>11:38</t>
-  </si>
-  <si>
-    <t>11:52</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>12:48</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>13:19</t>
-  </si>
-  <si>
-    <t>12:19</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>13:29</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>13:52</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>12:42</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>13:33</t>
-  </si>
-  <si>
-    <t>14:03</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>14:23</t>
-  </si>
-  <si>
-    <t>13:14</t>
-  </si>
-  <si>
-    <t>13:28</t>
-  </si>
-  <si>
-    <t>13:41</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>14:24</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>13:34</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>14:01</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>14:44</t>
-  </si>
-  <si>
-    <t>15:07</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>14:27</t>
-  </si>
-  <si>
-    <t>14:51</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>15:21</t>
-  </si>
-  <si>
-    <t>15:33</t>
-  </si>
-  <si>
-    <t>15:41</t>
-  </si>
-  <si>
-    <t>14:29</t>
-  </si>
-  <si>
-    <t>14:43</t>
-  </si>
-  <si>
-    <t>14:56</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>15:39</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:02</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:04</t>
-  </si>
-  <si>
-    <t>15:17</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:11</t>
-  </si>
-  <si>
-    <t>16:23</t>
-  </si>
-  <si>
-    <t>16:31</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>15:56</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>16:39</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:02</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>16:24</t>
-  </si>
-  <si>
-    <t>16:37</t>
-  </si>
-  <si>
-    <t>17:03</t>
-  </si>
-  <si>
-    <t>17:24</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>17:47</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>17:04</t>
-  </si>
-  <si>
-    <t>17:17</t>
-  </si>
-  <si>
-    <t>17:43</t>
-  </si>
-  <si>
-    <t>18:04</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>18:27</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>17:34</t>
-  </si>
-  <si>
-    <t>18:13</t>
-  </si>
-  <si>
-    <t>18:34</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>18:57</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>18:02</t>
-  </si>
-  <si>
-    <t>18:16</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>19:16</t>
-  </si>
-  <si>
-    <t>19:27</t>
-  </si>
-  <si>
-    <t>19:39</t>
-  </si>
-  <si>
-    <t>19:47</t>
-  </si>
-  <si>
-    <t>18:48</t>
-  </si>
-  <si>
-    <t>19:01</t>
-  </si>
-  <si>
-    <t>19:48</t>
-  </si>
-  <si>
-    <t>19:59</t>
-  </si>
-  <si>
-    <t>20:11</t>
-  </si>
-  <si>
-    <t>20:19</t>
-  </si>
-  <si>
-    <t>19:06</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>19:33</t>
-  </si>
-  <si>
-    <t>19:57</t>
-  </si>
-  <si>
-    <t>20:16</t>
-  </si>
-  <si>
-    <t>20:27</t>
-  </si>
-  <si>
-    <t>20:39</t>
-  </si>
-  <si>
-    <t>20:47</t>
-  </si>
-  <si>
-    <t>19:38</t>
-  </si>
-  <si>
-    <t>19:52</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:29</t>
-  </si>
-  <si>
-    <t>20:48</t>
-  </si>
-  <si>
-    <t>20:59</t>
-  </si>
-  <si>
-    <t>21:11</t>
-  </si>
-  <si>
-    <t>21:19</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>20:24</t>
-  </si>
-  <si>
-    <t>20:37</t>
-  </si>
-  <si>
-    <t>21:01</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>21:31</t>
-  </si>
-  <si>
-    <t>21:43</t>
-  </si>
-  <si>
-    <t>21:51</t>
-  </si>
-  <si>
-    <t>20:42</t>
-  </si>
-  <si>
-    <t>20:56</t>
-  </si>
-  <si>
-    <t>21:09</t>
-  </si>
-  <si>
-    <t>21:33</t>
-  </si>
-  <si>
-    <t>21:52</t>
-  </si>
-  <si>
-    <t>22:03</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>22:23</t>
-  </si>
-  <si>
-    <t>21:14</t>
-  </si>
-  <si>
-    <t>21:28</t>
-  </si>
-  <si>
-    <t>21:41</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>22:24</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>22:47</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>21:44</t>
-  </si>
-  <si>
-    <t>21:57</t>
-  </si>
-  <si>
-    <t>22:21</t>
-  </si>
-  <si>
-    <t>22:39</t>
-  </si>
-  <si>
-    <t>22:49</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>23:07</t>
-  </si>
-  <si>
-    <t>320번(평일)</t>
-  </si>
-  <si>
-    <t>하귀(수산)-하귀초등학교-하귀휴먼시아1,2단지-외도부영1,2차아파트
-  -도평(성지요양원)-광평(노형성당)-제주한라대학교-제주고/중흥s클래스 
-  -제주제일고등학교-롯데마트-연동365의원-민오름(연북로)-한라도서관입구
-  -구산마을-탐라중학교-한일베라체-동광초등학교(신천동)-거로사거리
-  -화북공업단지-화북휴먼시아-드림마트-오름중-삼화초교-휴먼시아정문</t>
-  </si>
-  <si>
-    <t>수산(하귀)→연북로→삼화지구</t>
-  </si>
-  <si>
-    <t>첫차 6:14(노형성당 출발), 막차 21:30, 배차간격 5~74분, 삼영교통(064-713-7000)</t>
-  </si>
-  <si>
-    <t>(시행일 : 2024.2.23.)</t>
-  </si>
-  <si>
     <t>삼화초등학교</t>
   </si>
   <si>
@@ -812,13 +30,31 @@
     <t>근로복지공단(연삼로)</t>
   </si>
   <si>
+    <t>제주여고(정문)</t>
+  </si>
+  <si>
+    <t>롯데마트</t>
+  </si>
+  <si>
+    <t>외도부영</t>
+  </si>
+  <si>
     <t>하귀휴먼시아
 아파트</t>
   </si>
   <si>
+    <t>수산(하귀)</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
     <t>06:00</t>
   </si>
   <si>
+    <t>06:10</t>
+  </si>
+  <si>
     <t>06:22</t>
   </si>
   <si>
@@ -831,6 +67,15 @@
     <t>07:02</t>
   </si>
   <si>
+    <t>07:11</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>06:25</t>
   </si>
   <si>
@@ -840,7 +85,13 @@
     <t>06:49</t>
   </si>
   <si>
+    <t>07:01</t>
+  </si>
+  <si>
     <t>07:44</t>
+  </si>
+  <si>
+    <t>07:58</t>
   </si>
   <si>
     <t>08:01
@@ -853,27 +104,42 @@
     <t>07:08</t>
   </si>
   <si>
+    <t>07:24</t>
+  </si>
+  <si>
     <t>07:36</t>
   </si>
   <si>
     <t>07:57</t>
   </si>
   <si>
+    <t>08:23</t>
+  </si>
+  <si>
     <t>08:37</t>
   </si>
   <si>
+    <t>08:50</t>
+  </si>
+  <si>
     <t>07:17</t>
   </si>
   <si>
     <t>07:27</t>
   </si>
   <si>
+    <t>07:43</t>
+  </si>
+  <si>
     <t>07:55</t>
   </si>
   <si>
     <t>08:16</t>
   </si>
   <si>
+    <t>08:42</t>
+  </si>
+  <si>
     <t>08:56</t>
   </si>
   <si>
@@ -883,9 +149,15 @@
     <t>07:42</t>
   </si>
   <si>
+    <t>07:52</t>
+  </si>
+  <si>
     <t>08:08</t>
   </si>
   <si>
+    <t>08:20</t>
+  </si>
+  <si>
     <t>08:41</t>
   </si>
   <si>
@@ -895,12 +167,21 @@
     <t>09:21</t>
   </si>
   <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
     <t>08:21</t>
   </si>
   <si>
     <t>08:49</t>
   </si>
   <si>
+    <t>09:10</t>
+  </si>
+  <si>
     <t>09:36</t>
   </si>
   <si>
@@ -913,6 +194,9 @@
     <t>08:53</t>
   </si>
   <si>
+    <t>09:03</t>
+  </si>
+  <si>
     <t>09:17</t>
   </si>
   <si>
@@ -931,6 +215,9 @@
     <t>10:39</t>
   </si>
   <si>
+    <t>09:16</t>
+  </si>
+  <si>
     <t>09:26</t>
   </si>
   <si>
@@ -940,6 +227,9 @@
     <t>09:52</t>
   </si>
   <si>
+    <t>10:11</t>
+  </si>
+  <si>
     <t>10:35</t>
   </si>
   <si>
@@ -1006,30 +296,66 @@
     <t>10:59</t>
   </si>
   <si>
+    <t>11:23</t>
+  </si>
+  <si>
     <t>11:50</t>
   </si>
   <si>
     <t>10:19</t>
   </si>
   <si>
+    <t>10:29</t>
+  </si>
+  <si>
     <t>10:43</t>
   </si>
   <si>
     <t>11:14</t>
   </si>
   <si>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
     <t>11:00</t>
   </si>
   <si>
     <t>11:36</t>
   </si>
   <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
     <t>11:51</t>
   </si>
   <si>
     <t>12:01</t>
   </si>
   <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
     <t>13:24</t>
   </si>
   <si>
@@ -1039,6 +365,12 @@
     <t>12:23</t>
   </si>
   <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
     <t>13:18</t>
   </si>
   <si>
@@ -1057,12 +389,18 @@
     <t>13:05</t>
   </si>
   <si>
+    <t>13:19</t>
+  </si>
+  <si>
     <t>13:31</t>
   </si>
   <si>
     <t>13:50</t>
   </si>
   <si>
+    <t>14:14</t>
+  </si>
+  <si>
     <t>14:28</t>
   </si>
   <si>
@@ -1075,6 +413,9 @@
     <t>13:51</t>
   </si>
   <si>
+    <t>14:03</t>
+  </si>
+  <si>
     <t>14:22</t>
   </si>
   <si>
@@ -1099,12 +440,30 @@
     <t>15:05</t>
   </si>
   <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>15:43</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
     <t>15:25</t>
   </si>
   <si>
+    <t>15:39</t>
+  </si>
+  <si>
     <t>15:51</t>
   </si>
   <si>
+    <t>16:10</t>
+  </si>
+  <si>
     <t>16:34</t>
   </si>
   <si>
@@ -1132,9 +491,15 @@
     <t>16:49</t>
   </si>
   <si>
+    <t>17:03</t>
+  </si>
+  <si>
     <t>17:16</t>
   </si>
   <si>
+    <t>15:50</t>
+  </si>
+  <si>
     <t>16:04</t>
   </si>
   <si>
@@ -1162,6 +527,12 @@
     <t>16:19</t>
   </si>
   <si>
+    <t>16:31</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
     <t>17:14</t>
   </si>
   <si>
@@ -1171,15 +542,24 @@
     <t>17:41</t>
   </si>
   <si>
+    <t>16:20</t>
+  </si>
+  <si>
     <t>16:36</t>
   </si>
   <si>
     <t>17:09</t>
   </si>
   <si>
+    <t>17:35</t>
+  </si>
+  <si>
     <t>17:49</t>
   </si>
   <si>
+    <t>18:02</t>
+  </si>
+  <si>
     <t>16:30</t>
   </si>
   <si>
@@ -1195,6 +575,9 @@
     <t>17:29</t>
   </si>
   <si>
+    <t>17:55</t>
+  </si>
+  <si>
     <t>18:09</t>
   </si>
   <si>
@@ -1219,6 +602,9 @@
     <t>18:20</t>
   </si>
   <si>
+    <t>18:34</t>
+  </si>
+  <si>
     <t>18:47</t>
   </si>
   <si>
@@ -1237,6 +623,9 @@
     <t>18:39</t>
   </si>
   <si>
+    <t>19:05</t>
+  </si>
+  <si>
     <t>19:19</t>
   </si>
   <si>
@@ -1258,6 +647,12 @@
     <t>20:02</t>
   </si>
   <si>
+    <t>20:16</t>
+  </si>
+  <si>
+    <t>20:29</t>
+  </si>
+  <si>
     <t>19:29</t>
   </si>
   <si>
@@ -1288,6 +683,9 @@
     <t>20:15</t>
   </si>
   <si>
+    <t>20:27</t>
+  </si>
+  <si>
     <t>20:46</t>
   </si>
   <si>
@@ -1306,6 +704,12 @@
     <t>20:33</t>
   </si>
   <si>
+    <t>20:47</t>
+  </si>
+  <si>
+    <t>20:59</t>
+  </si>
+  <si>
     <t>21:18</t>
   </si>
   <si>
@@ -1319,6 +723,12 @@
   </si>
   <si>
     <t>20:55</t>
+  </si>
+  <si>
+    <t>21:19</t>
+  </si>
+  <si>
+    <t>21:31</t>
   </si>
   <si>
     <t>21:50</t>
@@ -1335,6 +745,21 @@
  종료)</t>
   </si>
   <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>21:44</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>22:39</t>
+  </si>
+  <si>
     <t>22:53</t>
   </si>
   <si>
@@ -1361,6 +786,9 @@
     <t>23:08
 (하귀하나로
  종료)</t>
+  </si>
+  <si>
+    <t>320번(평일)</t>
   </si>
   <si>
     <t>삼화초등학교-오름중학교-거로마을-거로사거리-근로복지공단-한일베라체
@@ -1380,14 +808,576 @@
     <t>(시행일 : 2024.2.23)</t>
   </si>
   <si>
-    <t>제주여고
-(정문)</t>
-  </si>
-  <si>
-    <t>화북휴먼시아 정문</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>하귀휴먼시아</t>
+  </si>
+  <si>
+    <t>근로복지공단
+(연삼로)</t>
+  </si>
+  <si>
+    <t>화북휴먼시아</t>
+  </si>
+  <si>
+    <t>화북휴먼시아
+ 정문</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>06:14
+(노형성당 출발)</t>
+  </si>
+  <si>
+    <t>06:21</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>06:51</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>06:37</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>07:09</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>07:22</t>
+  </si>
+  <si>
+    <t>07:48</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>07:19</t>
+  </si>
+  <si>
+    <t>07:32</t>
+  </si>
+  <si>
+    <t>08:19</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>08:24</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:47</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>07:18</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>09:18</t>
+  </si>
+  <si>
+    <t>08:17
+(하귀하나로)</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>09:27</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>09:47</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>11:43</t>
+  </si>
+  <si>
+    <t>10:34</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>13:52</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>13:33</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>13:41</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>14:24</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
+    <t>15:33</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>14:56</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>16:39</t>
+  </si>
+  <si>
+    <t>17:02</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>16:24</t>
+  </si>
+  <si>
+    <t>16:37</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>17:47</t>
+  </si>
+  <si>
+    <t>17:04</t>
+  </si>
+  <si>
+    <t>17:17</t>
+  </si>
+  <si>
+    <t>17:43</t>
+  </si>
+  <si>
+    <t>18:04</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>18:27</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>17:34</t>
+  </si>
+  <si>
+    <t>18:13</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>18:57</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>18:29</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>19:16</t>
+  </si>
+  <si>
+    <t>19:27</t>
+  </si>
+  <si>
+    <t>19:39</t>
+  </si>
+  <si>
+    <t>19:47</t>
+  </si>
+  <si>
+    <t>18:48</t>
+  </si>
+  <si>
+    <t>19:01</t>
+  </si>
+  <si>
+    <t>19:48</t>
+  </si>
+  <si>
+    <t>19:59</t>
+  </si>
+  <si>
+    <t>20:11</t>
+  </si>
+  <si>
+    <t>20:19</t>
+  </si>
+  <si>
+    <t>19:06</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>19:33</t>
+  </si>
+  <si>
+    <t>19:57</t>
+  </si>
+  <si>
+    <t>20:39</t>
+  </si>
+  <si>
+    <t>19:38</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:48</t>
+  </si>
+  <si>
+    <t>21:11</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>20:24</t>
+  </si>
+  <si>
+    <t>20:37</t>
+  </si>
+  <si>
+    <t>21:01</t>
+  </si>
+  <si>
+    <t>21:43</t>
+  </si>
+  <si>
+    <t>21:51</t>
+  </si>
+  <si>
+    <t>20:42</t>
+  </si>
+  <si>
+    <t>20:56</t>
+  </si>
+  <si>
+    <t>21:09</t>
+  </si>
+  <si>
+    <t>21:33</t>
+  </si>
+  <si>
+    <t>21:52</t>
+  </si>
+  <si>
+    <t>22:03</t>
+  </si>
+  <si>
+    <t>22:23</t>
+  </si>
+  <si>
+    <t>21:14</t>
+  </si>
+  <si>
+    <t>21:28</t>
+  </si>
+  <si>
+    <t>21:41</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>22:24</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>22:47</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>21:57</t>
+  </si>
+  <si>
+    <t>22:21</t>
+  </si>
+  <si>
+    <t>22:49</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>23:07</t>
+  </si>
+  <si>
+    <t>하귀(수산)-하귀초등학교-하귀휴먼시아1,2단지-외도부영1,2차아파트
+  -도평(성지요양원)-광평(노형성당)-제주한라대학교-제주고/중흥s클래스 
+  -제주제일고등학교-롯데마트-연동365의원-민오름(연북로)-한라도서관입구
+  -구산마을-탐라중학교-한일베라체-동광초등학교(신천동)-거로사거리
+  -화북공업단지-화북휴먼시아-드림마트-오름중-삼화초교-휴먼시아정문</t>
+  </si>
+  <si>
+    <t>수산(하귀)→연북로→삼화지구</t>
+  </si>
+  <si>
+    <t>첫차 6:14(노형성당 출발), 막차 21:30, 배차간격 5~74분, 삼영교통(064-713-7000)</t>
+  </si>
+  <si>
+    <t>(시행일 : 2024.2.23.)</t>
   </si>
   <si>
     <t>06:20</t>
@@ -1396,94 +1386,103 @@
     <t>06:34</t>
   </si>
   <si>
-    <t>06:47</t>
+    <t>07:41</t>
+  </si>
+  <si>
+    <t>07:54</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>07:04</t>
+  </si>
+  <si>
+    <t>07:23</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>08:29</t>
   </si>
   <si>
     <t>07:30</t>
   </si>
   <si>
-    <t>07:39</t>
-  </si>
-  <si>
-    <t>07:59</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>08:14</t>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>09:14</t>
+  </si>
+  <si>
+    <t>08:10</t>
   </si>
   <si>
     <t>08:34</t>
   </si>
   <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:54</t>
-  </si>
-  <si>
-    <t>08:07</t>
-  </si>
-  <si>
-    <t>08:31</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>09:11</t>
-  </si>
-  <si>
-    <t>09:19</t>
-  </si>
-  <si>
-    <t>08:44</t>
-  </si>
-  <si>
-    <t>09:49</t>
-  </si>
-  <si>
-    <t>10:09</t>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>09:00</t>
   </si>
   <si>
     <t>09:24</t>
   </si>
   <si>
-    <t>09:37</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>11:21</t>
-  </si>
-  <si>
-    <t>11:29</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>10:58</t>
-  </si>
-  <si>
-    <t>11:41</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>11:26</t>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>10:21</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>09:54</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>11:49</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>12:40</t>
   </si>
   <si>
     <t>11:39</t>
@@ -1492,415 +1491,139 @@
     <t>12:03</t>
   </si>
   <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>13:23</t>
+  </si>
+  <si>
     <t>12:22</t>
   </si>
   <si>
-    <t>12:31</t>
-  </si>
-  <si>
-    <t>12:43</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>12:44</t>
-  </si>
-  <si>
-    <t>13:03</t>
-  </si>
-  <si>
-    <t>13:12</t>
-  </si>
-  <si>
-    <t>13:32</t>
-  </si>
-  <si>
-    <t>12:34</t>
-  </si>
-  <si>
-    <t>13:01</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>13:44</t>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:39</t>
   </si>
   <si>
     <t>13:53</t>
   </si>
   <si>
-    <t>14:13</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
     <t>14:06</t>
   </si>
   <si>
-    <t>14:54</t>
-  </si>
-  <si>
-    <t>15:06</t>
-  </si>
-  <si>
-    <t>15:27</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>14:37</t>
-  </si>
-  <si>
-    <t>15:28</t>
-  </si>
-  <si>
-    <t>15:47</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>15:18</t>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>14:12</t>
+  </si>
+  <si>
+    <t>15:19</t>
   </si>
   <si>
     <t>15:32</t>
   </si>
   <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>16:09</t>
-  </si>
-  <si>
-    <t>16:28</t>
-  </si>
-  <si>
-    <t>16:57</t>
-  </si>
-  <si>
-    <t>15:59</t>
-  </si>
-  <si>
-    <t>16:13</t>
-  </si>
-  <si>
-    <t>16:26</t>
-  </si>
-  <si>
-    <t>17:18</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>17:38</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>17:07</t>
-  </si>
-  <si>
-    <t>17:31</t>
-  </si>
-  <si>
-    <t>17:59</t>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>15:24</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>15:14</t>
+  </si>
+  <si>
+    <t>15:38</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>16:58</t>
+  </si>
+  <si>
+    <t>15:57</t>
+  </si>
+  <si>
+    <t>16:21</t>
+  </si>
+  <si>
+    <t>17:57</t>
   </si>
   <si>
     <t>18:11</t>
   </si>
   <si>
-    <t>18:19</t>
-  </si>
-  <si>
-    <t>17:48</t>
-  </si>
-  <si>
-    <t>18:12</t>
-  </si>
-  <si>
-    <t>18:31</t>
+    <t>18:24</t>
+  </si>
+  <si>
+    <t>17:23</t>
   </si>
   <si>
     <t>18:40</t>
   </si>
   <si>
-    <t>18:52</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>18:53</t>
-  </si>
-  <si>
-    <t>19:12</t>
-  </si>
-  <si>
-    <t>19:21</t>
-  </si>
-  <si>
-    <t>19:41</t>
-  </si>
-  <si>
-    <t>18:43</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>19:34</t>
-  </si>
-  <si>
-    <t>19:53</t>
-  </si>
-  <si>
-    <t>20:22</t>
-  </si>
-  <si>
-    <t>19:24</t>
-  </si>
-  <si>
-    <t>20:34</t>
-  </si>
-  <si>
-    <t>20:43</t>
+    <t>18:54</t>
+  </si>
+  <si>
+    <t>19:07</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>18:59</t>
+  </si>
+  <si>
+    <t>19:23</t>
+  </si>
+  <si>
+    <t>19:37</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>18:49</t>
+  </si>
+  <si>
+    <t>19:13</t>
+  </si>
+  <si>
+    <t>19:42</t>
+  </si>
+  <si>
+    <t>20:06</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>19:56</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>20:49</t>
   </si>
   <si>
     <t>21:03</t>
-  </si>
-  <si>
-    <t>20:32</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>21:36</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>21:13</t>
-  </si>
-  <si>
-    <t>22:17</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>320번(토,공휴일)</t>
-  </si>
-  <si>
-    <t>첫차 6:14(노형성당 출발), 막차 21:30, 배차간격 35~44분, 삼영교통(064-713-7000)</t>
-  </si>
-  <si>
-    <t>(시행일 : 2024.02.23.)</t>
-  </si>
-  <si>
-    <t>07:41</t>
-  </si>
-  <si>
-    <t>06:54</t>
-  </si>
-  <si>
-    <t>07:04</t>
-  </si>
-  <si>
-    <t>07:23</t>
-  </si>
-  <si>
-    <t>08:01</t>
-  </si>
-  <si>
-    <t>08:29</t>
-  </si>
-  <si>
-    <t>08:04</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>09:14</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>09:44</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>10:21</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>09:54</t>
-  </si>
-  <si>
-    <t>10:23</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>10:13</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>10:56</t>
-  </si>
-  <si>
-    <t>11:49</t>
-  </si>
-  <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>13:23</t>
-  </si>
-  <si>
-    <t>13:39</t>
-  </si>
-  <si>
-    <t>13:58</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>14:49</t>
-  </si>
-  <si>
-    <t>14:12</t>
-  </si>
-  <si>
-    <t>15:19</t>
-  </si>
-  <si>
-    <t>14:31</t>
-  </si>
-  <si>
-    <t>15:24</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>15:14</t>
-  </si>
-  <si>
-    <t>15:38</t>
-  </si>
-  <si>
-    <t>16:07</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>16:58</t>
-  </si>
-  <si>
-    <t>15:57</t>
-  </si>
-  <si>
-    <t>16:21</t>
-  </si>
-  <si>
-    <t>17:57</t>
-  </si>
-  <si>
-    <t>18:24</t>
-  </si>
-  <si>
-    <t>17:23</t>
-  </si>
-  <si>
-    <t>18:54</t>
-  </si>
-  <si>
-    <t>19:07</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>18:59</t>
-  </si>
-  <si>
-    <t>19:23</t>
-  </si>
-  <si>
-    <t>19:37</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>18:49</t>
-  </si>
-  <si>
-    <t>19:13</t>
-  </si>
-  <si>
-    <t>19:42</t>
-  </si>
-  <si>
-    <t>20:06</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>19:56</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>20:49</t>
   </si>
   <si>
     <t>21:16</t>
@@ -1933,6 +1656,9 @@
   <si>
     <t>23:08
 (하귀하나로 종료)</t>
+  </si>
+  <si>
+    <t>320번(토,공휴일)</t>
   </si>
   <si>
     <t>삼화초등학교-오름중학교-거로마을-거로사거리-근로복지공단-한일베라체
@@ -1944,6 +1670,280 @@
   </si>
   <si>
     <t>첫차 6:10, 막차 21:40, 배차간격 20~43분, 삼영교통(064-713-7000)</t>
+  </si>
+  <si>
+    <t>제주여고
+(정문)</t>
+  </si>
+  <si>
+    <t>화북휴먼시아 정문</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>07:59</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>08:31</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>09:11</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>09:49</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>09:37</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>11:41</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>12:31</t>
+  </si>
+  <si>
+    <t>12:43</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>13:03</t>
+  </si>
+  <si>
+    <t>13:12</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>13:44</t>
+  </si>
+  <si>
+    <t>14:13</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>15:27</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>15:28</t>
+  </si>
+  <si>
+    <t>15:47</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>15:18</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>16:09</t>
+  </si>
+  <si>
+    <t>16:28</t>
+  </si>
+  <si>
+    <t>16:57</t>
+  </si>
+  <si>
+    <t>15:59</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>16:26</t>
+  </si>
+  <si>
+    <t>17:18</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>17:38</t>
+  </si>
+  <si>
+    <t>16:54</t>
+  </si>
+  <si>
+    <t>17:07</t>
+  </si>
+  <si>
+    <t>17:31</t>
+  </si>
+  <si>
+    <t>17:59</t>
+  </si>
+  <si>
+    <t>18:19</t>
+  </si>
+  <si>
+    <t>17:48</t>
+  </si>
+  <si>
+    <t>18:12</t>
+  </si>
+  <si>
+    <t>18:31</t>
+  </si>
+  <si>
+    <t>18:52</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>18:53</t>
+  </si>
+  <si>
+    <t>19:12</t>
+  </si>
+  <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>19:41</t>
+  </si>
+  <si>
+    <t>18:43</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>19:34</t>
+  </si>
+  <si>
+    <t>19:53</t>
+  </si>
+  <si>
+    <t>20:22</t>
+  </si>
+  <si>
+    <t>19:24</t>
+  </si>
+  <si>
+    <t>20:34</t>
+  </si>
+  <si>
+    <t>20:43</t>
+  </si>
+  <si>
+    <t>20:32</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>21:36</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>21:13</t>
+  </si>
+  <si>
+    <t>22:17</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>첫차 6:14(노형성당 출발), 막차 21:30, 배차간격 35~44분, 삼영교통(064-713-7000)</t>
+  </si>
+  <si>
+    <t>(시행일 : 2024.02.23.)</t>
   </si>
 </sst>
 </file>
@@ -2588,28 +2588,28 @@
         <v>10</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -2617,19 +2617,19 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>23</v>
@@ -2641,7 +2641,7 @@
         <v>25</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -2673,7 +2673,7 @@
         <v>33</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -2684,28 +2684,28 @@
         <v>34</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -2713,31 +2713,31 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -2745,31 +2745,31 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -2777,31 +2777,31 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -2809,31 +2809,31 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -2841,31 +2841,31 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -2873,31 +2873,31 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -2905,31 +2905,31 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>86</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -2937,31 +2937,31 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -2969,31 +2969,31 @@
         <v>13.0</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -3001,31 +3001,31 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F21" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="H21" s="12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -3033,31 +3033,31 @@
         <v>15.0</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" ht="40.0" customHeight="true">
@@ -3065,31 +3065,31 @@
         <v>16.0</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="40.0" customHeight="true">
@@ -3097,31 +3097,31 @@
         <v>17.0</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="40.0" customHeight="true">
@@ -3129,31 +3129,31 @@
         <v>18.0</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="40.0" customHeight="true">
@@ -3161,31 +3161,31 @@
         <v>19.0</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" ht="40.0" customHeight="true">
@@ -3193,31 +3193,31 @@
         <v>20.0</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" ht="40.0" customHeight="true">
@@ -3225,31 +3225,31 @@
         <v>21.0</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" ht="40.0" customHeight="true">
@@ -3257,31 +3257,31 @@
         <v>22.0</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" ht="40.0" customHeight="true">
@@ -3289,31 +3289,31 @@
         <v>23.0</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" ht="40.0" customHeight="true">
@@ -3321,31 +3321,31 @@
         <v>24.0</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" ht="40.0" customHeight="true">
@@ -3353,31 +3353,31 @@
         <v>25.0</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" ht="40.0" customHeight="true">
@@ -3385,31 +3385,31 @@
         <v>26.0</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" ht="40.0" customHeight="true">
@@ -3417,31 +3417,31 @@
         <v>27.0</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" ht="40.0" customHeight="true">
@@ -3449,31 +3449,31 @@
         <v>28.0</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" ht="40.0" customHeight="true">
@@ -3481,31 +3481,31 @@
         <v>29.0</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" ht="40.0" customHeight="true">
@@ -3513,31 +3513,31 @@
         <v>30.0</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" ht="40.0" customHeight="true">
@@ -3545,31 +3545,31 @@
         <v>31.0</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" ht="40.0" customHeight="true">
@@ -3577,31 +3577,31 @@
         <v>32.0</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" ht="40.0" customHeight="true">
@@ -3609,16 +3609,16 @@
         <v>33.0</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="G40" s="15" t="s">
         <v>250</v>
@@ -3633,7 +3633,7 @@
         <v>253</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3740,13 +3740,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>260</v>
-      </c>
       <c r="E7" s="25" t="s">
-        <v>261</v>
+        <v>6</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>5</v>
@@ -3755,13 +3755,13 @@
         <v>4</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>3</v>
+        <v>260</v>
       </c>
       <c r="I7" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="J7" s="25" t="s">
         <v>262</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>1</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>9</v>
@@ -3775,7 +3775,7 @@
         <v>263</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>264</v>
@@ -3790,13 +3790,13 @@
         <v>267</v>
       </c>
       <c r="I8" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="J8" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="28" t="s">
-        <v>22</v>
-      </c>
       <c r="K8" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -3804,7 +3804,7 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
       <c r="D9" s="28" t="s">
         <v>269</v>
@@ -3813,22 +3813,22 @@
         <v>270</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H9" s="28" t="s">
         <v>271</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J9" s="28" t="s">
         <v>272</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -3842,25 +3842,25 @@
         <v>274</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>50</v>
+        <v>275</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>276</v>
+        <v>43</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>33</v>
+        <v>277</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -3868,31 +3868,31 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>24</v>
+        <v>280</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K11" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -3900,31 +3900,31 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>288</v>
+        <v>39</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -3932,31 +3932,31 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>289</v>
+        <v>28</v>
       </c>
       <c r="E13" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="F13" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>290</v>
-      </c>
       <c r="G13" s="28" t="s">
-        <v>65</v>
+        <v>292</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K13" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -3964,31 +3964,31 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>60</v>
+        <v>287</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>296</v>
+        <v>50</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="H14" s="28" t="s">
         <v>298</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>300</v>
+        <v>58</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -3996,31 +3996,31 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>70</v>
+        <v>276</v>
       </c>
       <c r="D15" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="F15" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="G15" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="I15" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>304</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>306</v>
-      </c>
       <c r="K15" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -4028,31 +4028,31 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D16" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="I16" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="G16" s="28" t="s">
+      <c r="J16" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="H16" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>312</v>
-      </c>
       <c r="K16" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -4060,31 +4060,31 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="I17" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="J17" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="E17" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>320</v>
-      </c>
       <c r="K17" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -4092,31 +4092,31 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>323</v>
+        <v>95</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -4124,31 +4124,31 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>103</v>
       </c>
       <c r="I19" s="28" t="s">
-        <v>104</v>
+        <v>324</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -4156,31 +4156,31 @@
         <v>13.0</v>
       </c>
       <c r="C20" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="I20" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="28" t="s">
-        <v>112</v>
-      </c>
       <c r="J20" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -4188,31 +4188,31 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="H21" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="I21" s="28" t="s">
         <v>333</v>
       </c>
-      <c r="E21" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>334</v>
-      </c>
       <c r="J21" s="28" t="s">
-        <v>335</v>
+        <v>123</v>
       </c>
       <c r="K21" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -4220,31 +4220,31 @@
         <v>15.0</v>
       </c>
       <c r="C22" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="I22" s="28" t="s">
         <v>336</v>
       </c>
-      <c r="D22" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="28" t="s">
+      <c r="J22" s="28" t="s">
         <v>337</v>
       </c>
-      <c r="H22" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>339</v>
-      </c>
-      <c r="J22" s="28" t="s">
-        <v>340</v>
-      </c>
       <c r="K22" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" ht="40.0" customHeight="true">
@@ -4252,31 +4252,31 @@
         <v>16.0</v>
       </c>
       <c r="C23" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="F23" s="28" t="s">
         <v>341</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="G23" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="28" t="s">
         <v>342</v>
       </c>
-      <c r="E23" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="28" t="s">
+      <c r="J23" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G23" s="28" t="s">
-        <v>344</v>
-      </c>
-      <c r="H23" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>345</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>346</v>
-      </c>
       <c r="K23" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="40.0" customHeight="true">
@@ -4284,31 +4284,31 @@
         <v>17.0</v>
       </c>
       <c r="C24" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="F24" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="E24" s="28" t="s">
+      <c r="G24" s="28" t="s">
         <v>348</v>
       </c>
-      <c r="F24" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="G24" s="28" t="s">
+      <c r="H24" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="I24" s="28" t="s">
         <v>350</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="J24" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="J24" s="28" t="s">
-        <v>352</v>
-      </c>
       <c r="K24" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="40.0" customHeight="true">
@@ -4316,31 +4316,31 @@
         <v>18.0</v>
       </c>
       <c r="C25" s="28" t="s">
+        <v>352</v>
+      </c>
+      <c r="D25" s="28" t="s">
         <v>353</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="E25" s="28" t="s">
         <v>354</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="F25" s="28" t="s">
         <v>355</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>350</v>
       </c>
       <c r="G25" s="28" t="s">
         <v>356</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>163</v>
+        <v>351</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="K25" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="40.0" customHeight="true">
@@ -4348,31 +4348,31 @@
         <v>19.0</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>140</v>
+        <v>337</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>357</v>
+        <v>126</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>152</v>
+        <v>358</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>155</v>
+        <v>360</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I26" s="28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K26" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" ht="40.0" customHeight="true">
@@ -4380,31 +4380,31 @@
         <v>20.0</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>366</v>
+        <v>145</v>
       </c>
       <c r="H27" s="28" t="s">
-        <v>367</v>
+        <v>159</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>173</v>
+        <v>368</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>368</v>
+        <v>147</v>
       </c>
       <c r="K27" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" ht="40.0" customHeight="true">
@@ -4412,31 +4412,31 @@
         <v>21.0</v>
       </c>
       <c r="C28" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>370</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="F28" s="28" t="s">
         <v>363</v>
       </c>
-      <c r="D28" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>369</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>370</v>
-      </c>
       <c r="G28" s="28" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>374</v>
+        <v>169</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" ht="40.0" customHeight="true">
@@ -4444,31 +4444,31 @@
         <v>22.0</v>
       </c>
       <c r="C29" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="G29" s="28" t="s">
         <v>375</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="H29" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I29" s="28" t="s">
         <v>376</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="J29" s="28" t="s">
         <v>377</v>
       </c>
-      <c r="F29" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="H29" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="J29" s="28" t="s">
-        <v>380</v>
-      </c>
       <c r="K29" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" ht="40.0" customHeight="true">
@@ -4476,31 +4476,31 @@
         <v>23.0</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>166</v>
+        <v>378</v>
       </c>
       <c r="E30" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="I30" s="28" t="s">
         <v>381</v>
       </c>
-      <c r="F30" s="28" t="s">
-        <v>360</v>
-      </c>
-      <c r="G30" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="I30" s="28" t="s">
-        <v>383</v>
-      </c>
       <c r="J30" s="28" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K30" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" ht="40.0" customHeight="true">
@@ -4508,31 +4508,31 @@
         <v>24.0</v>
       </c>
       <c r="C31" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="F31" s="28" t="s">
         <v>384</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="G31" s="28" t="s">
         <v>385</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="H31" s="28" t="s">
         <v>386</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="I31" s="28" t="s">
         <v>387</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="J31" s="28" t="s">
         <v>388</v>
       </c>
-      <c r="H31" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="I31" s="28" t="s">
-        <v>389</v>
-      </c>
-      <c r="J31" s="28" t="s">
-        <v>390</v>
-      </c>
       <c r="K31" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" ht="40.0" customHeight="true">
@@ -4540,31 +4540,31 @@
         <v>25.0</v>
       </c>
       <c r="C32" s="28" t="s">
+        <v>389</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="F32" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="G32" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="I32" s="28" t="s">
         <v>393</v>
       </c>
-      <c r="F32" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="G32" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>188</v>
-      </c>
       <c r="J32" s="28" t="s">
-        <v>397</v>
+        <v>201</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" ht="40.0" customHeight="true">
@@ -4572,31 +4572,31 @@
         <v>26.0</v>
       </c>
       <c r="C33" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="H33" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="I33" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="J33" s="28" t="s">
         <v>400</v>
       </c>
-      <c r="F33" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="G33" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" s="28" t="s">
-        <v>403</v>
-      </c>
-      <c r="J33" s="28" t="s">
-        <v>404</v>
-      </c>
       <c r="K33" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" ht="40.0" customHeight="true">
@@ -4604,31 +4604,31 @@
         <v>27.0</v>
       </c>
       <c r="C34" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>401</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="I34" s="28" t="s">
         <v>405</v>
       </c>
-      <c r="D34" s="28" t="s">
-        <v>397</v>
-      </c>
-      <c r="E34" s="28" t="s">
+      <c r="J34" s="28" t="s">
         <v>406</v>
       </c>
-      <c r="F34" s="28" t="s">
-        <v>407</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="H34" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="J34" s="28" t="s">
-        <v>217</v>
-      </c>
       <c r="K34" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" ht="40.0" customHeight="true">
@@ -4636,31 +4636,31 @@
         <v>28.0</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D35" s="28" t="s">
+        <v>408</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="F35" s="28" t="s">
         <v>410</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="G35" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="I35" s="28" t="s">
         <v>411</v>
       </c>
-      <c r="F35" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="G35" s="28" t="s">
-        <v>413</v>
-      </c>
-      <c r="H35" s="28" t="s">
-        <v>414</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>415</v>
-      </c>
       <c r="J35" s="28" t="s">
-        <v>416</v>
+        <v>228</v>
       </c>
       <c r="K35" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" ht="40.0" customHeight="true">
@@ -4668,31 +4668,31 @@
         <v>29.0</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>421</v>
+        <v>229</v>
       </c>
       <c r="I36" s="28" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J36" s="28" t="s">
-        <v>423</v>
+        <v>235</v>
       </c>
       <c r="K36" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" ht="40.0" customHeight="true">
@@ -4700,31 +4700,31 @@
         <v>30.0</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>213</v>
+        <v>419</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>219</v>
+        <v>420</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>426</v>
+        <v>241</v>
       </c>
       <c r="H37" s="28" t="s">
-        <v>427</v>
+        <v>236</v>
       </c>
       <c r="I37" s="28" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="J37" s="28" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="K37" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" ht="40.0" customHeight="true">
@@ -4732,31 +4732,31 @@
         <v>31.0</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>221</v>
+        <v>425</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>227</v>
+        <v>426</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="I38" s="28" t="s">
-        <v>433</v>
+        <v>244</v>
       </c>
       <c r="J38" s="28" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="K38" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" ht="40.0" customHeight="true">
@@ -4764,31 +4764,31 @@
         <v>32.0</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>226</v>
+        <v>430</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>246</v>
+        <v>431</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>247</v>
+        <v>432</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="H39" s="28" t="s">
-        <v>250</v>
+        <v>435</v>
       </c>
       <c r="I39" s="28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J39" s="28" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K39" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" ht="40.0" customHeight="true">
@@ -4796,19 +4796,19 @@
         <v>33.0</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>437</v>
+        <v>242</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>431</v>
+        <v>243</v>
       </c>
       <c r="E40" s="31" t="s">
         <v>438</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G40" s="31" t="s">
-        <v>439</v>
+        <v>245</v>
       </c>
       <c r="H40" s="31" t="s">
         <v>440</v>
@@ -4820,7 +4820,7 @@
         <v>442</v>
       </c>
       <c r="K40" s="32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4854,13 +4854,13 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="33" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
       <c r="E2" s="33"/>
       <c r="F2" s="35" t="s">
-        <v>255</v>
+        <v>540</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="37" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -4906,7 +4906,7 @@
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" s="39" t="s">
-        <v>556</v>
+        <v>446</v>
       </c>
       <c r="K5"/>
     </row>
@@ -4933,22 +4933,22 @@
         <v>2</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>3</v>
+        <v>260</v>
       </c>
       <c r="F7" s="41" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>447</v>
+        <v>5</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>261</v>
+        <v>6</v>
       </c>
       <c r="I7" s="41" t="s">
         <v>7</v>
       </c>
       <c r="J7" s="41" t="s">
-        <v>448</v>
+        <v>8</v>
       </c>
       <c r="K7" s="42" t="s">
         <v>9</v>
@@ -4959,31 +4959,31 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>447</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>448</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="44" t="s">
         <v>449</v>
       </c>
-      <c r="D8" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="I8" s="44" t="s">
-        <v>21</v>
-      </c>
       <c r="J8" s="44" t="s">
-        <v>28</v>
+        <v>450</v>
       </c>
       <c r="K8" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -4991,31 +4991,31 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>450</v>
+        <v>13</v>
       </c>
       <c r="D9" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" s="44" t="s">
         <v>451</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="F9" s="44" t="s">
         <v>452</v>
-      </c>
-      <c r="F9" s="44" t="s">
-        <v>16</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>453</v>
       </c>
       <c r="H9" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="I9" s="44" t="s">
         <v>454</v>
-      </c>
-      <c r="I9" s="44" t="s">
-        <v>25</v>
       </c>
       <c r="J9" s="44" t="s">
         <v>455</v>
       </c>
       <c r="K9" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -5023,31 +5023,31 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>35</v>
+        <v>280</v>
       </c>
       <c r="F10" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>278</v>
+      </c>
+      <c r="I10" s="44" t="s">
         <v>456</v>
       </c>
-      <c r="G10" s="44" t="s">
-        <v>457</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>458</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>63</v>
-      </c>
       <c r="J10" s="44" t="s">
-        <v>459</v>
+        <v>39</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -5055,31 +5055,31 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="44" t="s">
+        <v>457</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>458</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>450</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>459</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="I11" s="44" t="s">
         <v>460</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="J11" s="44" t="s">
         <v>461</v>
       </c>
-      <c r="E11" s="44" t="s">
-        <v>462</v>
-      </c>
-      <c r="F11" s="44" t="s">
-        <v>463</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>464</v>
-      </c>
-      <c r="I11" s="44" t="s">
-        <v>465</v>
-      </c>
-      <c r="J11" s="44" t="s">
-        <v>466</v>
-      </c>
       <c r="K11" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -5087,31 +5087,31 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>46</v>
+        <v>300</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>69</v>
+        <v>292</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>288</v>
+        <v>463</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>302</v>
+        <v>57</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>468</v>
+        <v>59</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>314</v>
+        <v>464</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="K12" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -5119,31 +5119,31 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D13" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>461</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>468</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>469</v>
+      </c>
+      <c r="I13" s="44" t="s">
         <v>470</v>
       </c>
-      <c r="E13" s="44" t="s">
-        <v>471</v>
-      </c>
-      <c r="F13" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="G13" s="44" t="s">
-        <v>472</v>
-      </c>
-      <c r="H13" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="44" t="s">
-        <v>78</v>
-      </c>
       <c r="J13" s="44" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="K13" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -5151,31 +5151,31 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>292</v>
+        <v>471</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>321</v>
+        <v>67</v>
       </c>
       <c r="E14" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="44" t="s">
         <v>473</v>
       </c>
-      <c r="F14" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>330</v>
-      </c>
       <c r="H14" s="44" t="s">
-        <v>311</v>
+        <v>474</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>474</v>
+        <v>314</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>475</v>
+        <v>97</v>
       </c>
       <c r="K14" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -5183,31 +5183,31 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>309</v>
+        <v>475</v>
       </c>
       <c r="D15" s="44" t="s">
+        <v>473</v>
+      </c>
+      <c r="E15" s="44" t="s">
         <v>476</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="F15" s="44" t="s">
+        <v>474</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="H15" s="44" t="s">
         <v>477</v>
       </c>
-      <c r="F15" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>478</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>326</v>
-      </c>
       <c r="I15" s="44" t="s">
-        <v>479</v>
+        <v>323</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>480</v>
+        <v>328</v>
       </c>
       <c r="K15" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -5215,31 +5215,31 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>84</v>
+        <v>478</v>
       </c>
       <c r="D16" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>477</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>479</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>480</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="E16" s="44" t="s">
-        <v>482</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>483</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>484</v>
-      </c>
-      <c r="H16" s="44" t="s">
-        <v>485</v>
-      </c>
-      <c r="I16" s="44" t="s">
-        <v>486</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>487</v>
-      </c>
       <c r="K16" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -5247,31 +5247,31 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>93</v>
+        <v>479</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>492</v>
+        <v>339</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>334</v>
+        <v>111</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="K17" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -5279,31 +5279,31 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>107</v>
+        <v>484</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>495</v>
+        <v>106</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>496</v>
+        <v>339</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="H18" s="44" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>129</v>
+        <v>489</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -5311,31 +5311,31 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>500</v>
+        <v>122</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>115</v>
+        <v>487</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>137</v>
+        <v>491</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>355</v>
+        <v>132</v>
       </c>
       <c r="I19" s="44" t="s">
-        <v>350</v>
+        <v>492</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="K19" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -5343,31 +5343,31 @@
         <v>13.0</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>353</v>
+        <v>491</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>125</v>
+        <v>494</v>
       </c>
       <c r="F20" s="44" t="s">
         <v>132</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>503</v>
+        <v>128</v>
       </c>
       <c r="H20" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="K20" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -5375,31 +5375,31 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>157</v>
+        <v>351</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>507</v>
+        <v>139</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="H21" s="44" t="s">
-        <v>165</v>
+        <v>499</v>
       </c>
       <c r="I21" s="44" t="s">
-        <v>509</v>
+        <v>368</v>
       </c>
       <c r="J21" s="44" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="K21" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -5407,31 +5407,31 @@
         <v>15.0</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I22" s="44" t="s">
-        <v>367</v>
+        <v>504</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="K22" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" ht="40.0" customHeight="true">
@@ -5439,31 +5439,31 @@
         <v>16.0</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>382</v>
+        <v>170</v>
       </c>
       <c r="H23" s="44" t="s">
-        <v>519</v>
+        <v>171</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>520</v>
+        <v>172</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>521</v>
+        <v>173</v>
       </c>
       <c r="K23" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="40.0" customHeight="true">
@@ -5471,31 +5471,31 @@
         <v>17.0</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>385</v>
+        <v>181</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>522</v>
+        <v>170</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>523</v>
+        <v>382</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>524</v>
+        <v>171</v>
       </c>
       <c r="G24" s="44" t="s">
-        <v>399</v>
+        <v>191</v>
       </c>
       <c r="H24" s="44" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="I24" s="44" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="J24" s="44" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="K24" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="40.0" customHeight="true">
@@ -5503,31 +5503,31 @@
         <v>18.0</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>393</v>
+        <v>511</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>528</v>
+        <v>381</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>530</v>
+        <v>394</v>
       </c>
       <c r="H25" s="44" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="J25" s="44" t="s">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="K25" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="40.0" customHeight="true">
@@ -5535,31 +5535,31 @@
         <v>19.0</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>193</v>
+        <v>394</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>194</v>
+        <v>515</v>
       </c>
       <c r="F26" s="44" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="H26" s="44" t="s">
-        <v>536</v>
+        <v>517</v>
       </c>
       <c r="I26" s="44" t="s">
-        <v>208</v>
+        <v>518</v>
       </c>
       <c r="J26" s="44" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="K26" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" ht="40.0" customHeight="true">
@@ -5567,31 +5567,31 @@
         <v>20.0</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>190</v>
+        <v>516</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="G27" s="44" t="s">
-        <v>541</v>
+        <v>522</v>
       </c>
       <c r="H27" s="44" t="s">
-        <v>409</v>
+        <v>523</v>
       </c>
       <c r="I27" s="44" t="s">
-        <v>413</v>
+        <v>524</v>
       </c>
       <c r="J27" s="44" t="s">
-        <v>542</v>
+        <v>227</v>
       </c>
       <c r="K27" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" ht="40.0" customHeight="true">
@@ -5599,31 +5599,31 @@
         <v>21.0</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>543</v>
+        <v>203</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>214</v>
+        <v>522</v>
       </c>
       <c r="E28" s="44" t="s">
-        <v>417</v>
+        <v>525</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>419</v>
+        <v>523</v>
       </c>
       <c r="G28" s="44" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="H28" s="44" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="I28" s="44" t="s">
-        <v>430</v>
+        <v>528</v>
       </c>
       <c r="J28" s="44" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="K28" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" ht="40.0" customHeight="true">
@@ -5631,31 +5631,31 @@
         <v>22.0</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>205</v>
+        <v>526</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>547</v>
+        <v>411</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>231</v>
+        <v>527</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="H29" s="44" t="s">
-        <v>422</v>
+        <v>531</v>
       </c>
       <c r="I29" s="44" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>247</v>
+        <v>533</v>
       </c>
       <c r="K29" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" ht="40.0" customHeight="true">
@@ -5663,31 +5663,31 @@
         <v>23.0</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>420</v>
+        <v>534</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>423</v>
+        <v>531</v>
       </c>
       <c r="G30" s="44" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H30" s="44" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I30" s="44" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="J30" s="44" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="K30" s="45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" ht="40.0" customHeight="true">
@@ -5695,16 +5695,16 @@
         <v>24.0</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F31" s="47" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="G31" s="47" t="s">
         <v>250</v>
@@ -5716,10 +5716,10 @@
         <v>252</v>
       </c>
       <c r="J31" s="47" t="s">
-        <v>253</v>
+        <v>538</v>
       </c>
       <c r="K31" s="48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -5753,13 +5753,13 @@
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="49" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
       <c r="E2" s="49"/>
       <c r="F2" s="51" t="s">
-        <v>631</v>
+        <v>443</v>
       </c>
       <c r="G2" s="49"/>
       <c r="H2" s="49"/>
@@ -5795,7 +5795,7 @@
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="53" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -5805,7 +5805,7 @@
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" s="55" t="s">
-        <v>258</v>
+        <v>632</v>
       </c>
       <c r="K5"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="57" t="s">
         <v>259</v>
-      </c>
-      <c r="D7" s="57" t="s">
-        <v>260</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>6</v>
@@ -5838,16 +5838,16 @@
         <v>5</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>4</v>
+        <v>542</v>
       </c>
       <c r="H7" s="57" t="s">
         <v>3</v>
       </c>
       <c r="I7" s="57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J7" s="57" t="s">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="K7" s="58" t="s">
         <v>9</v>
@@ -5858,31 +5858,31 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>18</v>
+        <v>544</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="E8" s="60" t="s">
-        <v>451</v>
+        <v>264</v>
       </c>
       <c r="F8" s="60" t="s">
+        <v>265</v>
+      </c>
+      <c r="G8" s="60" t="s">
         <v>266</v>
       </c>
-      <c r="G8" s="60" t="s">
-        <v>15</v>
-      </c>
       <c r="H8" s="60" t="s">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="I8" s="60" t="s">
-        <v>557</v>
+        <v>22</v>
       </c>
       <c r="J8" s="60" t="s">
-        <v>461</v>
+        <v>275</v>
       </c>
       <c r="K8" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" ht="40.0" customHeight="true">
@@ -5890,31 +5890,31 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="60" t="s">
-        <v>265</v>
+        <v>447</v>
       </c>
       <c r="D9" s="60" t="s">
-        <v>13</v>
+        <v>448</v>
       </c>
       <c r="E9" s="60" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="F9" s="60" t="s">
-        <v>559</v>
+        <v>16</v>
       </c>
       <c r="G9" s="60" t="s">
-        <v>560</v>
+        <v>457</v>
       </c>
       <c r="H9" s="60" t="s">
-        <v>61</v>
+        <v>546</v>
       </c>
       <c r="I9" s="60" t="s">
-        <v>561</v>
+        <v>272</v>
       </c>
       <c r="J9" s="60" t="s">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="K9" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="40.0" customHeight="true">
@@ -5922,31 +5922,31 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="60" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D10" s="60" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E10" s="60" t="s">
-        <v>35</v>
+        <v>280</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>43</v>
+        <v>548</v>
       </c>
       <c r="G10" s="60" t="s">
-        <v>25</v>
+        <v>549</v>
       </c>
       <c r="H10" s="60" t="s">
-        <v>32</v>
+        <v>455</v>
       </c>
       <c r="I10" s="60" t="s">
-        <v>562</v>
+        <v>301</v>
       </c>
       <c r="J10" s="60" t="s">
-        <v>47</v>
+        <v>463</v>
       </c>
       <c r="K10" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" ht="40.0" customHeight="true">
@@ -5954,31 +5954,31 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="60" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D11" s="60" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="E11" s="60" t="s">
-        <v>461</v>
+        <v>550</v>
       </c>
       <c r="F11" s="60" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="G11" s="60" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="60" t="s">
-        <v>54</v>
+        <v>552</v>
       </c>
       <c r="I11" s="60" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="J11" s="60" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="K11" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" ht="40.0" customHeight="true">
@@ -5986,31 +5986,31 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>62</v>
+        <v>289</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="E12" s="60" t="s">
-        <v>52</v>
+        <v>306</v>
       </c>
       <c r="F12" s="60" t="s">
-        <v>459</v>
+        <v>48</v>
       </c>
       <c r="G12" s="60" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="H12" s="60" t="s">
-        <v>295</v>
+        <v>556</v>
       </c>
       <c r="I12" s="60" t="s">
-        <v>567</v>
+        <v>80</v>
       </c>
       <c r="J12" s="60" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="K12" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="40.0" customHeight="true">
@@ -6018,31 +6018,31 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="60" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" s="60" t="s">
-        <v>569</v>
+        <v>467</v>
       </c>
       <c r="E13" s="60" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F13" s="60" t="s">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="G13" s="60" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="H13" s="60" t="s">
-        <v>571</v>
+        <v>95</v>
       </c>
       <c r="I13" s="60" t="s">
-        <v>572</v>
+        <v>312</v>
       </c>
       <c r="J13" s="60" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="K13" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="40.0" customHeight="true">
@@ -6050,31 +6050,31 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="60" t="s">
-        <v>573</v>
+        <v>55</v>
       </c>
       <c r="D14" s="60" t="s">
-        <v>302</v>
+        <v>87</v>
       </c>
       <c r="E14" s="60" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="F14" s="60" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="G14" s="60" t="s">
-        <v>575</v>
+        <v>101</v>
       </c>
       <c r="H14" s="60" t="s">
-        <v>576</v>
+        <v>77</v>
       </c>
       <c r="I14" s="60" t="s">
-        <v>80</v>
+        <v>561</v>
       </c>
       <c r="J14" s="60" t="s">
-        <v>329</v>
+        <v>562</v>
       </c>
       <c r="K14" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="40.0" customHeight="true">
@@ -6082,31 +6082,31 @@
         <v>8.0</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>577</v>
+        <v>75</v>
       </c>
       <c r="D15" s="60" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="E15" s="60" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="F15" s="60" t="s">
-        <v>576</v>
+        <v>78</v>
       </c>
       <c r="G15" s="60" t="s">
-        <v>95</v>
+        <v>565</v>
       </c>
       <c r="H15" s="60" t="s">
-        <v>579</v>
+        <v>93</v>
       </c>
       <c r="I15" s="60" t="s">
-        <v>91</v>
+        <v>566</v>
       </c>
       <c r="J15" s="60" t="s">
-        <v>98</v>
+        <v>567</v>
       </c>
       <c r="K15" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="40.0" customHeight="true">
@@ -6114,31 +6114,31 @@
         <v>9.0</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>580</v>
+        <v>317</v>
       </c>
       <c r="D16" s="60" t="s">
-        <v>95</v>
+        <v>568</v>
       </c>
       <c r="E16" s="60" t="s">
-        <v>96</v>
+        <v>482</v>
       </c>
       <c r="F16" s="60" t="s">
-        <v>579</v>
+        <v>483</v>
       </c>
       <c r="G16" s="60" t="s">
-        <v>581</v>
+        <v>486</v>
       </c>
       <c r="H16" s="60" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="I16" s="60" t="s">
-        <v>100</v>
+        <v>570</v>
       </c>
       <c r="J16" s="60" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="K16" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" ht="40.0" customHeight="true">
@@ -6146,31 +6146,31 @@
         <v>10.0</v>
       </c>
       <c r="C17" s="60" t="s">
-        <v>482</v>
+        <v>572</v>
       </c>
       <c r="D17" s="60" t="s">
-        <v>581</v>
+        <v>324</v>
       </c>
       <c r="E17" s="60" t="s">
-        <v>483</v>
+        <v>573</v>
       </c>
       <c r="F17" s="60" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="G17" s="60" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="H17" s="60" t="s">
-        <v>120</v>
+        <v>576</v>
       </c>
       <c r="I17" s="60" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J17" s="60" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="K17" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="40.0" customHeight="true">
@@ -6178,31 +6178,31 @@
         <v>11.0</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>484</v>
+        <v>578</v>
       </c>
       <c r="D18" s="60" t="s">
-        <v>584</v>
+        <v>332</v>
       </c>
       <c r="E18" s="60" t="s">
-        <v>113</v>
+        <v>579</v>
       </c>
       <c r="F18" s="60" t="s">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="G18" s="60" t="s">
-        <v>500</v>
+        <v>581</v>
       </c>
       <c r="H18" s="60" t="s">
-        <v>586</v>
+        <v>489</v>
       </c>
       <c r="I18" s="60" t="s">
-        <v>498</v>
+        <v>347</v>
       </c>
       <c r="J18" s="60" t="s">
-        <v>501</v>
+        <v>582</v>
       </c>
       <c r="K18" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="40.0" customHeight="true">
@@ -6210,31 +6210,31 @@
         <v>12.0</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>342</v>
+        <v>487</v>
       </c>
       <c r="D19" s="60" t="s">
-        <v>500</v>
+        <v>334</v>
       </c>
       <c r="E19" s="60" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F19" s="60" t="s">
-        <v>586</v>
+        <v>490</v>
       </c>
       <c r="G19" s="60" t="s">
-        <v>587</v>
+        <v>355</v>
       </c>
       <c r="H19" s="60" t="s">
-        <v>349</v>
+        <v>138</v>
       </c>
       <c r="I19" s="60" t="s">
-        <v>588</v>
+        <v>133</v>
       </c>
       <c r="J19" s="60" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="K19" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" ht="40.0" customHeight="true">
@@ -6242,31 +6242,31 @@
         <v>13.0</v>
       </c>
       <c r="C20" s="60" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D20" s="60" t="s">
-        <v>587</v>
+        <v>136</v>
       </c>
       <c r="E20" s="60" t="s">
-        <v>590</v>
+        <v>343</v>
       </c>
       <c r="F20" s="60" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G20" s="60" t="s">
-        <v>346</v>
+        <v>584</v>
       </c>
       <c r="H20" s="60" t="s">
-        <v>356</v>
+        <v>143</v>
       </c>
       <c r="I20" s="60" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="J20" s="60" t="s">
-        <v>511</v>
+        <v>586</v>
       </c>
       <c r="K20" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="40.0" customHeight="true">
@@ -6274,31 +6274,31 @@
         <v>14.0</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="D21" s="60" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="E21" s="60" t="s">
-        <v>133</v>
+        <v>370</v>
       </c>
       <c r="F21" s="60" t="s">
-        <v>356</v>
+        <v>588</v>
       </c>
       <c r="G21" s="60" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="H21" s="60" t="s">
-        <v>594</v>
+        <v>142</v>
       </c>
       <c r="I21" s="60" t="s">
-        <v>154</v>
+        <v>590</v>
       </c>
       <c r="J21" s="60" t="s">
-        <v>595</v>
+        <v>161</v>
       </c>
       <c r="K21" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" ht="40.0" customHeight="true">
@@ -6306,31 +6306,31 @@
         <v>15.0</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D22" s="60" t="s">
+        <v>496</v>
+      </c>
+      <c r="E22" s="60" t="s">
+        <v>592</v>
+      </c>
+      <c r="F22" s="60" t="s">
         <v>593</v>
       </c>
-      <c r="E22" s="60" t="s">
-        <v>597</v>
-      </c>
-      <c r="F22" s="60" t="s">
+      <c r="G22" s="60" t="s">
         <v>594</v>
       </c>
-      <c r="G22" s="60" t="s">
-        <v>598</v>
-      </c>
       <c r="H22" s="60" t="s">
-        <v>162</v>
+        <v>379</v>
       </c>
       <c r="I22" s="60" t="s">
-        <v>599</v>
+        <v>156</v>
       </c>
       <c r="J22" s="60" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="K22" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" ht="40.0" customHeight="true">
@@ -6338,31 +6338,31 @@
         <v>16.0</v>
       </c>
       <c r="C23" s="60" t="s">
+        <v>596</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>597</v>
+      </c>
+      <c r="E23" s="60" t="s">
+        <v>598</v>
+      </c>
+      <c r="F23" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="60" t="s">
+        <v>599</v>
+      </c>
+      <c r="I23" s="60" t="s">
+        <v>600</v>
+      </c>
+      <c r="J23" s="60" t="s">
         <v>601</v>
       </c>
-      <c r="D23" s="60" t="s">
-        <v>598</v>
-      </c>
-      <c r="E23" s="60" t="s">
-        <v>602</v>
-      </c>
-      <c r="F23" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="G23" s="60" t="s">
-        <v>168</v>
-      </c>
-      <c r="H23" s="60" t="s">
-        <v>378</v>
-      </c>
-      <c r="I23" s="60" t="s">
-        <v>379</v>
-      </c>
-      <c r="J23" s="60" t="s">
-        <v>380</v>
-      </c>
       <c r="K23" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" ht="40.0" customHeight="true">
@@ -6370,31 +6370,31 @@
         <v>17.0</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>385</v>
+        <v>181</v>
       </c>
       <c r="D24" s="60" t="s">
-        <v>168</v>
+        <v>602</v>
       </c>
       <c r="E24" s="60" t="s">
-        <v>178</v>
+        <v>603</v>
       </c>
       <c r="F24" s="60" t="s">
-        <v>378</v>
+        <v>604</v>
       </c>
       <c r="G24" s="60" t="s">
-        <v>394</v>
+        <v>197</v>
       </c>
       <c r="H24" s="60" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I24" s="60" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="J24" s="60" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K24" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="40.0" customHeight="true">
@@ -6402,31 +6402,31 @@
         <v>18.0</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>605</v>
+        <v>190</v>
       </c>
       <c r="D25" s="60" t="s">
-        <v>394</v>
+        <v>177</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>176</v>
+        <v>607</v>
       </c>
       <c r="F25" s="60" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="G25" s="60" t="s">
-        <v>193</v>
+        <v>609</v>
       </c>
       <c r="H25" s="60" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="I25" s="60" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="J25" s="60" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="K25" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="40.0" customHeight="true">
@@ -6434,31 +6434,31 @@
         <v>19.0</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>400</v>
+        <v>179</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>193</v>
+        <v>394</v>
       </c>
       <c r="E26" s="60" t="s">
-        <v>608</v>
+        <v>395</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>531</v>
+        <v>612</v>
       </c>
       <c r="G26" s="60" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="H26" s="60" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>611</v>
+        <v>409</v>
       </c>
       <c r="J26" s="60" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K26" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" ht="40.0" customHeight="true">
@@ -6466,31 +6466,31 @@
         <v>20.0</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D27" s="60" t="s">
-        <v>609</v>
+        <v>393</v>
       </c>
       <c r="E27" s="60" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F27" s="60" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="G27" s="60" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="H27" s="60" t="s">
-        <v>616</v>
+        <v>208</v>
       </c>
       <c r="I27" s="60" t="s">
-        <v>617</v>
+        <v>214</v>
       </c>
       <c r="J27" s="60" t="s">
-        <v>425</v>
+        <v>620</v>
       </c>
       <c r="K27" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" ht="40.0" customHeight="true">
@@ -6498,31 +6498,31 @@
         <v>21.0</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>404</v>
+        <v>621</v>
       </c>
       <c r="D28" s="60" t="s">
-        <v>615</v>
+        <v>412</v>
       </c>
       <c r="E28" s="60" t="s">
-        <v>618</v>
+        <v>218</v>
       </c>
       <c r="F28" s="60" t="s">
-        <v>616</v>
+        <v>220</v>
       </c>
       <c r="G28" s="60" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="H28" s="60" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="I28" s="60" t="s">
-        <v>546</v>
+        <v>234</v>
       </c>
       <c r="J28" s="60" t="s">
-        <v>621</v>
+        <v>528</v>
       </c>
       <c r="K28" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" ht="40.0" customHeight="true">
@@ -6530,31 +6530,31 @@
         <v>22.0</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D29" s="60" t="s">
-        <v>619</v>
+        <v>406</v>
       </c>
       <c r="E29" s="60" t="s">
-        <v>212</v>
+        <v>624</v>
       </c>
       <c r="F29" s="60" t="s">
-        <v>620</v>
+        <v>424</v>
       </c>
       <c r="G29" s="60" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="H29" s="60" t="s">
-        <v>623</v>
+        <v>224</v>
       </c>
       <c r="I29" s="60" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="J29" s="60" t="s">
-        <v>625</v>
+        <v>243</v>
       </c>
       <c r="K29" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" ht="40.0" customHeight="true">
@@ -6562,31 +6562,31 @@
         <v>23.0</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>626</v>
+        <v>222</v>
       </c>
       <c r="D30" s="60" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E30" s="60" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F30" s="60" t="s">
-        <v>623</v>
+        <v>225</v>
       </c>
       <c r="G30" s="60" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="H30" s="60" t="s">
-        <v>236</v>
+        <v>433</v>
       </c>
       <c r="I30" s="60" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J30" s="60" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K30" s="61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" ht="40.0" customHeight="true">
@@ -6594,19 +6594,19 @@
         <v>24.0</v>
       </c>
       <c r="C31" s="63" t="s">
-        <v>437</v>
+        <v>242</v>
       </c>
       <c r="D31" s="63" t="s">
-        <v>431</v>
+        <v>243</v>
       </c>
       <c r="E31" s="63" t="s">
         <v>438</v>
       </c>
       <c r="F31" s="63" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G31" s="63" t="s">
-        <v>439</v>
+        <v>245</v>
       </c>
       <c r="H31" s="63" t="s">
         <v>440</v>
@@ -6615,10 +6615,10 @@
         <v>441</v>
       </c>
       <c r="J31" s="63" t="s">
-        <v>630</v>
+        <v>442</v>
       </c>
       <c r="K31" s="64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
